--- a/SRS/SUCs.xlsx
+++ b/SRS/SUCs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d23393c4c06a5064/שולחן העבודה/Software studies/YEAR 2/פרוייקט גמר/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Uni\S_E\Handesaim\Year B\Semester A\Project\myProject\SRS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="330" documentId="11_6CA41F987706FC7CB4300D9FFD734D4F40BA830B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDE2CAC5-FBA1-484B-9B31-7B612CBEFE0E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2700F1-8AFF-4B0D-A2AC-64E0E36564FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2160" yWindow="2160" windowWidth="17280" windowHeight="8964" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="רשימה" sheetId="11" r:id="rId1"/>
@@ -176,50 +176,10 @@
     <t>דרישות פונקציונליות: 17</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>UC-7</t>
-    </r>
-  </si>
-  <si>
     <t>גישה למסך מדריך האפליקציה</t>
   </si>
   <si>
     <t>דרישות פונקציונליות: 20</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>UC-8</t>
-    </r>
   </si>
   <si>
     <t>דרישות פונקציונליות: 23,25  דרישות לא פונקיונליות: 24</t>
@@ -469,6 +429,34 @@
   </si>
   <si>
     <t xml:space="preserve">1. המשתמש יוצא מהאפליקציה              2. המערכת מפיקה דוח על נתוני המשתמש                                         3. המערכת שומרת את נתוני המשתמש בזכרון המכשיר                                           4.  המערכת מדווחת על נתוני המשתמש ל- FIREBASE              ה-FIREBASE עושה שימוש בנתונים לטובת הנפקת דוחות שימוש    </t>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>UC-6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>UC-7</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -964,16 +952,16 @@
     </row>
     <row r="2" spans="2:8" ht="18" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="E2" s="17" t="s">
         <v>85</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>87</v>
       </c>
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
@@ -981,16 +969,16 @@
     </row>
     <row r="3" spans="2:8" ht="36" x14ac:dyDescent="0.25">
       <c r="B3" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
@@ -998,7 +986,7 @@
     </row>
     <row r="4" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C4" s="22" t="s">
         <v>13</v>
@@ -1007,7 +995,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F4" s="18"/>
       <c r="G4" s="18"/>
@@ -1015,7 +1003,7 @@
     </row>
     <row r="5" spans="2:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>15</v>
@@ -1024,7 +1012,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F5" s="18"/>
       <c r="G5" s="18"/>
@@ -1032,7 +1020,7 @@
     </row>
     <row r="6" spans="2:8" ht="36" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>19</v>
@@ -1041,7 +1029,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F6" s="18"/>
       <c r="G6" s="18"/>
@@ -1058,7 +1046,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F7" s="18"/>
       <c r="G7" s="18"/>
@@ -1066,16 +1054,16 @@
     </row>
     <row r="8" spans="2:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>2</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
@@ -1083,16 +1071,16 @@
     </row>
     <row r="9" spans="2:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B9" s="21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>2</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
@@ -1100,16 +1088,16 @@
     </row>
     <row r="10" spans="2:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B10" s="21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>2</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F10" s="18"/>
       <c r="G10" s="18"/>
@@ -1117,16 +1105,16 @@
     </row>
     <row r="11" spans="2:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B11" s="21" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>2</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
@@ -1134,16 +1122,16 @@
     </row>
     <row r="12" spans="2:8" ht="36" x14ac:dyDescent="0.25">
       <c r="B12" s="21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>2</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
@@ -2165,10 +2153,10 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2192,7 +2180,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -2200,7 +2188,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -2208,7 +2196,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="198" x14ac:dyDescent="0.25">
@@ -2216,7 +2204,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -2230,7 +2218,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3245,10 +3233,10 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -3272,7 +3260,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -3280,7 +3268,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -3288,7 +3276,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="180" x14ac:dyDescent="0.25">
@@ -3296,7 +3284,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -4321,12 +4309,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:3" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
@@ -4342,7 +4330,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4350,7 +4338,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4358,7 +4346,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
@@ -4366,7 +4354,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="234" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4374,7 +4362,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="180.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4382,7 +4370,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5406,7 +5394,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -5430,7 +5418,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -5454,7 +5442,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="108.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -5462,7 +5450,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -5470,7 +5458,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6512,7 +6500,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -6520,7 +6508,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -6528,7 +6516,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="162" x14ac:dyDescent="0.25">
@@ -6536,7 +6524,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="72" x14ac:dyDescent="0.25">
@@ -6544,7 +6532,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -6552,7 +6540,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7602,7 +7590,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="54" x14ac:dyDescent="0.25">
@@ -7610,7 +7598,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="90" x14ac:dyDescent="0.25">
@@ -7618,7 +7606,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -8682,7 +8670,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -8690,7 +8678,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="162" x14ac:dyDescent="0.25">
@@ -8698,23 +8686,23 @@
         <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="126.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="108.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9764,7 +9752,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -9772,7 +9760,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
@@ -9780,7 +9768,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="216.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -9788,7 +9776,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -10817,10 +10805,10 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -10844,7 +10832,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -10852,7 +10840,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -10860,7 +10848,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="234" x14ac:dyDescent="0.25">
@@ -10868,7 +10856,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -10882,7 +10870,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11897,10 +11885,10 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11924,7 +11912,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -11932,7 +11920,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="54" x14ac:dyDescent="0.25">
@@ -11940,7 +11928,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="180" x14ac:dyDescent="0.25">
@@ -11948,23 +11936,23 @@
         <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="162.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="126.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -11972,7 +11960,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -12987,10 +12975,10 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -13014,7 +13002,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -13022,7 +13010,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -13030,7 +13018,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="162" x14ac:dyDescent="0.25">
@@ -13038,7 +13026,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -13052,7 +13040,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/SRS/SUCs.xlsx
+++ b/SRS/SUCs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Uni\S_E\Handesaim\Year B\Semester A\Project\myProject\SRS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\OneDrive - הקריה ללימודי הנדסה וטכנולוגיה\מסמכים\GitHub\CyberWall\SRS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2700F1-8AFF-4B0D-A2AC-64E0E36564FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460D9620-16CC-4ED9-AA90-47E468FA95A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="2160" windowWidth="17280" windowHeight="8964" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="רשימה" sheetId="11" r:id="rId1"/>
@@ -31,27 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="112">
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>UC-1</t>
-    </r>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="113">
   <si>
     <t>שחקנים ויעדים</t>
   </si>
@@ -456,6 +436,23 @@
         <rFont val="Calibri"/>
       </rPr>
       <t>UC-7</t>
+    </r>
+  </si>
+  <si>
+    <t>שינוי ממשק המשתמש</t>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>UC-1</t>
     </r>
   </si>
 </sst>
@@ -952,16 +949,16 @@
     </row>
     <row r="2" spans="2:8" ht="18" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="E2" s="17" t="s">
         <v>84</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>85</v>
       </c>
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
@@ -969,16 +966,16 @@
     </row>
     <row r="3" spans="2:8" ht="36" x14ac:dyDescent="0.25">
       <c r="B3" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
@@ -986,16 +983,16 @@
     </row>
     <row r="4" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F4" s="18"/>
       <c r="G4" s="18"/>
@@ -1003,16 +1000,16 @@
     </row>
     <row r="5" spans="2:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F5" s="18"/>
       <c r="G5" s="18"/>
@@ -1020,16 +1017,16 @@
     </row>
     <row r="6" spans="2:8" ht="36" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F6" s="18"/>
       <c r="G6" s="18"/>
@@ -1037,16 +1034,16 @@
     </row>
     <row r="7" spans="2:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="22" t="s">
-        <v>23</v>
-      </c>
       <c r="D7" s="20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F7" s="18"/>
       <c r="G7" s="18"/>
@@ -1054,16 +1051,16 @@
     </row>
     <row r="8" spans="2:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
@@ -1071,16 +1068,16 @@
     </row>
     <row r="9" spans="2:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B9" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
@@ -1088,16 +1085,16 @@
     </row>
     <row r="10" spans="2:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B10" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F10" s="18"/>
       <c r="G10" s="18"/>
@@ -1105,16 +1102,16 @@
     </row>
     <row r="11" spans="2:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="22" t="s">
-        <v>32</v>
-      </c>
       <c r="D11" s="20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
@@ -1122,16 +1119,16 @@
     </row>
     <row r="12" spans="2:8" ht="36" x14ac:dyDescent="0.25">
       <c r="B12" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="22" t="s">
-        <v>35</v>
-      </c>
       <c r="D12" s="20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
@@ -2153,72 +2150,72 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="198" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3233,69 +3230,69 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="180" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4"/>
     </row>
@@ -4311,71 +4308,71 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="234" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="180.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5"/>
     </row>
@@ -5391,74 +5388,74 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B2" s="8" t="s">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="108.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="234.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="108.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6473,74 +6470,74 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="162" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="72" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7555,72 +7552,72 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="54" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="90" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8635,82 +8632,82 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="162" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="126.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="108.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9725,72 +9722,72 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="216.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -10805,72 +10802,72 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="72" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="234" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11885,82 +11882,82 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="72" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="54" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="180" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="162.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="126.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -12975,72 +12972,72 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="162" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/SRS/SUCs.xlsx
+++ b/SRS/SUCs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\OneDrive - הקריה ללימודי הנדסה וטכנולוגיה\מסמכים\GitHub\CyberWall\SRS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d23393c4c06a5064/Documents/GitHub/CyberWall/SRS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460D9620-16CC-4ED9-AA90-47E468FA95A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{460D9620-16CC-4ED9-AA90-47E468FA95A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2F325CF-966A-4760-B9F0-00BD77D112CD}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5760" yWindow="3276" windowWidth="17280" windowHeight="8964" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="רשימה" sheetId="11" r:id="rId1"/>
@@ -25,13 +25,14 @@
     <sheet name="9" sheetId="9" r:id="rId10"/>
     <sheet name="10" sheetId="10" r:id="rId11"/>
     <sheet name="11" sheetId="12" r:id="rId12"/>
+    <sheet name="12" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="115">
   <si>
     <t>שחקנים ויעדים</t>
   </si>
@@ -162,9 +163,6 @@
     <t>דרישות פונקציונליות: 20</t>
   </si>
   <si>
-    <t>דרישות פונקציונליות: 23,25  דרישות לא פונקיונליות: 24</t>
-  </si>
-  <si>
     <t>SUC-8</t>
   </si>
   <si>
@@ -286,12 +284,6 @@
   </si>
   <si>
     <t>1. המשתמש מאשר הרשאה לאפליקציות המבקשות הרשאה                                   2.  המערכת קולטת את הלחיצה                                3. המכשיר מאפשר שימוש בהרשאה שהמשתמש אישר  4.האפליקציה יכולה להשתמש רק בהרשאות שהמשתמש אישר</t>
-  </si>
-  <si>
-    <t>חריגה מצעד 1 בMSS: לא אושר הרשאות לאפליקציה   2א1: האפליקציה לא תשתמש בשום הרשאות שלא אושרו                            2א2: האפליקציה תעשה שימוש בהרשאות שאושרו כם הם חלקיות, רק בחלק שהמשתמש אישר</t>
-  </si>
-  <si>
-    <t>חריגה מצעד 3 בMSS: משתמש רוצה לשנות הרשאה לאחר שאסר על שימוש בהרשאה זו                             3א1ץ משתמש יכול להסיר ולהפעיל הרשאות אפליקציות בכל רגע נתון</t>
   </si>
   <si>
     <t>שימוש במנגנון לכידת חבילות רשת</t>
@@ -454,6 +446,21 @@
       </rPr>
       <t>UC-1</t>
     </r>
+  </si>
+  <si>
+    <t>אישור הרשאות למיקרופון ומצלמה ע"י המשתמש</t>
+  </si>
+  <si>
+    <t>לחיצה על אישור הרשאה של המשתמש לאפליקציה המבקשת להשתמש במיקרופון ומצלמה</t>
+  </si>
+  <si>
+    <t>1. האפליקציה מופעלת במכשיר הסלולר                                         2. אפליקציה מבקשת הרשאה למיקרופון והמצלמה                                       3. המשתמש צריך לאשר את ההרשאות לשימוש במיקרופון והמצלמה במכשיר                                          4.  האפליקציה עושה שימוש במיקרופון והמצלמה                        5. המשמש יכול ב-ADVANCEMODE להסיר הרשאות</t>
+  </si>
+  <si>
+    <t>דרישות פונקציונליות: 30, 48-51  דרישות לא פונקיונליות: 29</t>
+  </si>
+  <si>
+    <t>אישור הרשאות למיקרופון ומצלמה</t>
   </si>
 </sst>
 </file>
@@ -949,16 +956,16 @@
     </row>
     <row r="2" spans="2:8" ht="18" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="17" t="s">
         <v>81</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>84</v>
       </c>
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
@@ -966,16 +973,16 @@
     </row>
     <row r="3" spans="2:8" ht="36" x14ac:dyDescent="0.25">
       <c r="B3" s="21" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
@@ -983,7 +990,7 @@
     </row>
     <row r="4" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C4" s="22" t="s">
         <v>12</v>
@@ -992,7 +999,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F4" s="18"/>
       <c r="G4" s="18"/>
@@ -1000,7 +1007,7 @@
     </row>
     <row r="5" spans="2:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>14</v>
@@ -1009,7 +1016,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F5" s="18"/>
       <c r="G5" s="18"/>
@@ -1017,7 +1024,7 @@
     </row>
     <row r="6" spans="2:8" ht="36" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>18</v>
@@ -1026,7 +1033,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F6" s="18"/>
       <c r="G6" s="18"/>
@@ -1043,7 +1050,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F7" s="18"/>
       <c r="G7" s="18"/>
@@ -1051,7 +1058,7 @@
     </row>
     <row r="8" spans="2:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>24</v>
@@ -1060,7 +1067,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
@@ -1068,16 +1075,16 @@
     </row>
     <row r="9" spans="2:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B9" s="21" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>1</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
@@ -1085,16 +1092,16 @@
     </row>
     <row r="10" spans="2:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B10" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>1</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F10" s="18"/>
       <c r="G10" s="18"/>
@@ -1102,16 +1109,16 @@
     </row>
     <row r="11" spans="2:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B11" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="22" t="s">
         <v>30</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>31</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>1</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
@@ -1119,16 +1126,16 @@
     </row>
     <row r="12" spans="2:8" ht="36" x14ac:dyDescent="0.25">
       <c r="B12" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="22" t="s">
         <v>33</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>34</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>1</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
@@ -2150,10 +2157,10 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2177,7 +2184,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -2185,7 +2192,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -2193,7 +2200,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="198" x14ac:dyDescent="0.25">
@@ -2201,7 +2208,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -2215,7 +2222,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3230,10 +3237,10 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -3257,7 +3264,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -3265,7 +3272,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -3273,7 +3280,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="180" x14ac:dyDescent="0.25">
@@ -3281,7 +3288,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -4308,10 +4315,10 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
@@ -4327,7 +4334,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4335,7 +4342,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4343,7 +4350,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
@@ -4351,7 +4358,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="234" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4359,7 +4366,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="180.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4367,7 +4374,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4375,6 +4382,1088 @@
         <v>10</v>
       </c>
       <c r="C10" s="5"/>
+    </row>
+    <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="6"/>
+    </row>
+    <row r="12" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A0425E6-E240-4790-A71F-96D2732F324C}">
+  <dimension ref="B1:C1000"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.59765625" customWidth="1"/>
+    <col min="2" max="2" width="22.19921875" customWidth="1"/>
+    <col min="3" max="3" width="28.5" customWidth="1"/>
+    <col min="4" max="26" width="8.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:3" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="61.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="234" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="180.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="42.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="6"/>
@@ -5388,10 +6477,10 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B2" s="8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -5415,7 +6504,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -5439,7 +6528,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="108.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -5447,7 +6536,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -5455,7 +6544,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6473,7 +7562,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -6497,7 +7586,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -6505,7 +7594,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -6513,7 +7602,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="162" x14ac:dyDescent="0.25">
@@ -6521,7 +7610,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="72" x14ac:dyDescent="0.25">
@@ -6529,7 +7618,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -6537,7 +7626,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7587,7 +8676,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="54" x14ac:dyDescent="0.25">
@@ -7595,7 +8684,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="90" x14ac:dyDescent="0.25">
@@ -7603,7 +8692,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -8667,7 +9756,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -8675,7 +9764,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="162" x14ac:dyDescent="0.25">
@@ -8683,23 +9772,23 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="126.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="108.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9749,7 +10838,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -9757,7 +10846,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
@@ -9765,7 +10854,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="216.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -9773,7 +10862,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -10802,7 +11891,7 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>24</v>
@@ -10829,7 +11918,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -10837,7 +11926,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -10845,7 +11934,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="234" x14ac:dyDescent="0.25">
@@ -10853,7 +11942,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -11870,7 +12959,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B1:C1001"/>
+  <dimension ref="B1:C999"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.59765625" customWidth="1"/>
@@ -11882,10 +12971,10 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11909,7 +12998,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -11917,7 +13006,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="54" x14ac:dyDescent="0.25">
@@ -11925,44 +13014,30 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="180" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" ht="180.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="162.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:3" ht="63.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="126.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>69</v>
-      </c>
+    <row r="10" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="6"/>
     </row>
-    <row r="11" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="6"/>
-    </row>
+    <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -12950,8 +14025,6 @@
     <row r="997" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="998" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="999" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1001" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
@@ -12972,10 +14045,10 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="36" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -12999,7 +14072,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -13007,7 +14080,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="36" x14ac:dyDescent="0.25">
@@ -13015,7 +14088,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="162" x14ac:dyDescent="0.25">
@@ -13023,7 +14096,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
@@ -13037,7 +14110,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/SRS/SUCs.xlsx
+++ b/SRS/SUCs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d23393c4c06a5064/Documents/GitHub/CyberWall/SRS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dariel\Documents\GitHub\CyberWall\SRS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{460D9620-16CC-4ED9-AA90-47E468FA95A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2F325CF-966A-4760-B9F0-00BD77D112CD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B04730A-6511-4A8A-97E9-CAAE2F9AA727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5760" yWindow="3276" windowWidth="17280" windowHeight="8964" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="רשימה" sheetId="11" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="116">
   <si>
     <t>שחקנים ויעדים</t>
   </si>
@@ -461,6 +461,9 @@
   </si>
   <si>
     <t>אישור הרשאות למיקרופון ומצלמה</t>
+  </si>
+  <si>
+    <t>SUC-12</t>
   </si>
 </sst>
 </file>
@@ -5395,7 +5398,7 @@
     <row r="1" spans="2:3" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:3" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>114</v>

--- a/SRS/SUCs.xlsx
+++ b/SRS/SUCs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dariel\Documents\GitHub\CyberWall\SRS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\OneDrive - הקריה ללימודי הנדסה וטכנולוגיה\מסמכים\GitHub\CyberWall\SRS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B04730A-6511-4A8A-97E9-CAAE2F9AA727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F16362-3B76-4EE8-A4B7-89585E34DC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="רשימה" sheetId="11" r:id="rId1"/>
